--- a/Nightdress-10177-EXTERNAL-MeeshoTemplate2PricesGSTIN-Copy.xlsx
+++ b/Nightdress-10177-EXTERNAL-MeeshoTemplate2PricesGSTIN-Copy.xlsx
@@ -2840,7 +2840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW147"/>
+  <dimension ref="A1:AW153"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
     <col width="15.8984375" customWidth="1" style="18" min="1" max="1"/>
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="D3" s="22" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E3" s="22">
         <f>IF(D3&gt;22,D3-22,"")</f>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="AC3" s="25" t="inlineStr">
         <is>
-          <t>/Pic/DE26030/Black/Black_1.png</t>
+          <t>https://example.com/test_front.jpg</t>
         </is>
       </c>
       <c r="AD3" s="25" t="inlineStr">
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="D4" s="22" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="E4" s="22">
         <f>IF(D4&gt;22,D4-22,"")</f>
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="D5" s="22" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="E5" s="22">
         <f>IF(D5&gt;22,D5-22,"")</f>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="D6" s="22" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="E6" s="22">
         <f>IF(D6&gt;22,D6-22,"")</f>
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="D7" s="22" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="E7" s="22">
         <f>IF(D7&gt;22,D7-22,"")</f>
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="D8" s="22" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="E8" s="22">
         <f>IF(D8&gt;22,D8-22,"")</f>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="D9" s="22" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="E9" s="22">
         <f>IF(D9&gt;22,D9-22,"")</f>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="D10" s="22" t="n">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="E10" s="22">
         <f>IF(D10&gt;22,D10-22,"")</f>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c r="D11" s="22" t="n">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="E11" s="22">
         <f>IF(D11&gt;22,D11-22,"")</f>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="D12" s="22" t="n">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="E12" s="22">
         <f>IF(D12&gt;22,D12-22,"")</f>
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="D13" s="22" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="E13" s="22">
         <f>IF(D13&gt;22,D13-22,"")</f>
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="D14" s="22" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="E14" s="22">
         <f>IF(D14&gt;22,D14-22,"")</f>
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="D15" s="22" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="E15" s="22">
         <f>IF(D15&gt;22,D15-22,"")</f>
@@ -6217,7 +6217,7 @@
         </is>
       </c>
       <c r="D16" s="22" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="E16" s="22">
         <f>IF(D16&gt;22,D16-22,"")</f>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="D17" s="22" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="E17" s="22">
         <f>IF(D17&gt;22,D17-22,"")</f>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="D18" s="22" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="E18" s="22">
         <f>IF(D18&gt;22,D18-22,"")</f>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="D19" s="22" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="E19" s="22">
         <f>IF(D19&gt;22,D19-22,"")</f>
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="D20" s="22" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="E20" s="22">
         <f>IF(D20&gt;22,D20-22,"")</f>
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="D21" s="22" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="E21" s="22">
         <f>IF(D21&gt;22,D21-22,"")</f>
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="D22" s="22" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="E22" s="22">
         <f>IF(D22&gt;22,D22-22,"")</f>
@@ -7718,7 +7718,7 @@
         </is>
       </c>
       <c r="D23" s="22" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="E23" s="22">
         <f>IF(D23&gt;22,D23-22,"")</f>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="D24" s="22" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="E24" s="22">
         <f>IF(D24&gt;22,D24-22,"")</f>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="D25" s="22" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="E25" s="22">
         <f>IF(D25&gt;22,D25-22,"")</f>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="D26" s="22" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="E26" s="22">
         <f>IF(D26&gt;22,D26-22,"")</f>
@@ -8574,7 +8574,7 @@
         </is>
       </c>
       <c r="D27" s="22" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="E27" s="22">
         <f>IF(D27&gt;22,D27-22,"")</f>
@@ -8789,7 +8789,7 @@
         </is>
       </c>
       <c r="D28" s="22" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="E28" s="22">
         <f>IF(D28&gt;22,D28-22,"")</f>
@@ -9004,7 +9004,7 @@
         </is>
       </c>
       <c r="D29" s="22" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="E29" s="22">
         <f>IF(D29&gt;22,D29-22,"")</f>
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="D30" s="22" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="E30" s="22">
         <f>IF(D30&gt;22,D30-22,"")</f>
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="D31" s="22" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="E31" s="22">
         <f>IF(D31&gt;22,D31-22,"")</f>
@@ -9645,7 +9645,7 @@
         </is>
       </c>
       <c r="D32" s="22" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="E32" s="22">
         <f>IF(D32&gt;22,D32-22,"")</f>
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="D33" s="22" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="E33" s="22">
         <f>IF(D33&gt;22,D33-22,"")</f>
@@ -10067,7 +10067,7 @@
         </is>
       </c>
       <c r="D34" s="22" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="E34" s="22">
         <f>IF(D34&gt;22,D34-22,"")</f>
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="D35" s="22" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="E35" s="22">
         <f>IF(D35&gt;22,D35-22,"")</f>
@@ -10493,7 +10493,7 @@
         </is>
       </c>
       <c r="D36" s="22" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="E36" s="22">
         <f>IF(D36&gt;22,D36-22,"")</f>
@@ -10708,7 +10708,7 @@
         </is>
       </c>
       <c r="D37" s="22" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="E37" s="22">
         <f>IF(D37&gt;22,D37-22,"")</f>
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="D38" s="22" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="E38" s="22">
         <f>IF(D38&gt;22,D38-22,"")</f>
@@ -11138,7 +11138,7 @@
         </is>
       </c>
       <c r="D39" s="22" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="E39" s="22">
         <f>IF(D39&gt;22,D39-22,"")</f>
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="D40" s="22" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="E40" s="22">
         <f>IF(D40&gt;22,D40-22,"")</f>
@@ -11568,7 +11568,7 @@
         </is>
       </c>
       <c r="D41" s="22" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="E41" s="22">
         <f>IF(D41&gt;22,D41-22,"")</f>
@@ -11783,7 +11783,7 @@
         </is>
       </c>
       <c r="D42" s="22" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="E42" s="22">
         <f>IF(D42&gt;22,D42-22,"")</f>
@@ -11998,7 +11998,7 @@
         </is>
       </c>
       <c r="D43" s="22" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="E43" s="22">
         <f>IF(D43&gt;22,D43-22,"")</f>
@@ -19585,7 +19585,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="E147">
         <f>IF(D147&gt;22,D147-22,"")</f>
@@ -19763,6 +19763,1156 @@
         </is>
       </c>
       <c r="AW147" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Stylish Comfortable, Cotton Nighty for Women, Nighty, 100% Cotton Nighty, Summer Nighty, Nighty for Ladies, Nighty for girls, Floral Nighty, Pure cotton nighty, Maxi, Gown, Soft breathable sleepwear, Skin Friendly Nightdress.</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148">
+        <f>IF(D148&gt;22,D148-22,"")</f>
+        <v/>
+      </c>
+      <c r="F148" t="n">
+        <v>449</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>285</v>
+      </c>
+      <c r="J148" t="n">
+        <v>6</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R148">
+        <f>IF(K148="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S148">
+        <f>IF(K148="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T148">
+        <f>IF(K148="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Blue_1_20260929_020509.jpg</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>DE26011N</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>DE26011N103613</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Upgrade your daily comfort with this printed nighty for women. Designed as a full-length maxi night gown, this sleeveless sleepwear offers a relaxed, flowing fit ideal for warm weather and daily home wear. The square neckline features contrast piping and a delicate center bow detail, complementing the all-over abstract print.</t>
+        </is>
+      </c>
+      <c r="AN148" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>Floral</t>
+        </is>
+      </c>
+      <c r="AT148" t="inlineStr">
+        <is>
+          <t>Short Sleeves</t>
+        </is>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149">
+        <f>IF(D149&gt;22,D149-22,"")</f>
+        <v/>
+      </c>
+      <c r="F149" t="n">
+        <v>499</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>285</v>
+      </c>
+      <c r="J149" t="n">
+        <v>10</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R149">
+        <f>IF(K149="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S149">
+        <f>IF(K149="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T149">
+        <f>IF(K149="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Teal</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>/Pic/DE26030/Black/Black_1.png</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>DE26_A6A560</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>DE26_A6A560103313</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Teal Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN149" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT149" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150">
+        <f>IF(D150&gt;22,D150-22,"")</f>
+        <v/>
+      </c>
+      <c r="F150" t="n">
+        <v>499</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>285</v>
+      </c>
+      <c r="J150" t="n">
+        <v>10</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R150">
+        <f>IF(K150="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S150">
+        <f>IF(K150="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T150">
+        <f>IF(K150="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>TESTDEL_032328</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>TESTDEL_032328103813</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Gold Maxi Women</t>
+        </is>
+      </c>
+      <c r="AN150" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT150" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>340</v>
+      </c>
+      <c r="E151">
+        <f>IF(D151&gt;22,D151-22,"")</f>
+        <v/>
+      </c>
+      <c r="F151" t="n">
+        <v>499</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>285</v>
+      </c>
+      <c r="J151" t="n">
+        <v>10</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R151">
+        <f>IF(K151="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S151">
+        <f>IF(K151="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T151">
+        <f>IF(K151="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Teal</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>/Pic/DE26030/Black/Black_1.png</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>DE26_C75AC4</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>DE26_C75AC4103313</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Teal Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN151" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT151" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>240</v>
+      </c>
+      <c r="E152">
+        <f>IF(D152&gt;22,D152-22,"")</f>
+        <v/>
+      </c>
+      <c r="F152" t="n">
+        <v>499</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>285</v>
+      </c>
+      <c r="J152" t="n">
+        <v>10</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R152">
+        <f>IF(K152="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S152">
+        <f>IF(K152="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T152">
+        <f>IF(K152="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>TESTDEL_A1CF0A</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>TESTDEL_A1CF0A103813</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Gold Maxi Women</t>
+        </is>
+      </c>
+      <c r="AN152" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT152" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>280</v>
+      </c>
+      <c r="E153">
+        <f>IF(D153&gt;22,D153-22,"")</f>
+        <v/>
+      </c>
+      <c r="F153" t="n">
+        <v>499</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>285</v>
+      </c>
+      <c r="J153" t="n">
+        <v>15</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R153">
+        <f>IF(K153="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S153">
+        <f>IF(K153="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T153">
+        <f>IF(K153="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_1.jpg</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_2.jpg</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_3.jpg</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_4.jpg</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>TESTIMG_AE9AB0</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>TESTIMG_AE9AB0103613</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Blue Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN153" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT153" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
         <is>
           <t>36</t>
         </is>

--- a/Nightdress-10177-EXTERNAL-MeeshoTemplate2PricesGSTIN-Copy.xlsx
+++ b/Nightdress-10177-EXTERNAL-MeeshoTemplate2PricesGSTIN-Copy.xlsx
@@ -2840,7 +2840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW153"/>
+  <dimension ref="A1:AW191"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
     <col width="15.8984375" customWidth="1" style="18" min="1" max="1"/>
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="D3" s="22" t="n">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E3" s="22">
         <f>IF(D3&gt;22,D3-22,"")</f>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="AC3" s="25" t="inlineStr">
         <is>
-          <t>https://example.com/test_front.jpg</t>
+          <t>/Pic/DE26030/Black/Black_1.png</t>
         </is>
       </c>
       <c r="AD3" s="25" t="inlineStr">
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="D4" s="22" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="E4" s="22">
         <f>IF(D4&gt;22,D4-22,"")</f>
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="D5" s="22" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="E5" s="22">
         <f>IF(D5&gt;22,D5-22,"")</f>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="D6" s="22" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="E6" s="22">
         <f>IF(D6&gt;22,D6-22,"")</f>
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="D7" s="22" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="E7" s="22">
         <f>IF(D7&gt;22,D7-22,"")</f>
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="D8" s="22" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="E8" s="22">
         <f>IF(D8&gt;22,D8-22,"")</f>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="D9" s="22" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="E9" s="22">
         <f>IF(D9&gt;22,D9-22,"")</f>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="D10" s="22" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="E10" s="22">
         <f>IF(D10&gt;22,D10-22,"")</f>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c r="D11" s="22" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="E11" s="22">
         <f>IF(D11&gt;22,D11-22,"")</f>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="D12" s="22" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="E12" s="22">
         <f>IF(D12&gt;22,D12-22,"")</f>
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="D13" s="22" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="E13" s="22">
         <f>IF(D13&gt;22,D13-22,"")</f>
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="D14" s="22" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="E14" s="22">
         <f>IF(D14&gt;22,D14-22,"")</f>
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="D15" s="22" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="E15" s="22">
         <f>IF(D15&gt;22,D15-22,"")</f>
@@ -6217,7 +6217,7 @@
         </is>
       </c>
       <c r="D16" s="22" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="E16" s="22">
         <f>IF(D16&gt;22,D16-22,"")</f>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="D17" s="22" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="E17" s="22">
         <f>IF(D17&gt;22,D17-22,"")</f>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="D18" s="22" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="E18" s="22">
         <f>IF(D18&gt;22,D18-22,"")</f>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="D19" s="22" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="E19" s="22">
         <f>IF(D19&gt;22,D19-22,"")</f>
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="D20" s="22" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="E20" s="22">
         <f>IF(D20&gt;22,D20-22,"")</f>
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="D21" s="22" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="E21" s="22">
         <f>IF(D21&gt;22,D21-22,"")</f>
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="D22" s="22" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="E22" s="22">
         <f>IF(D22&gt;22,D22-22,"")</f>
@@ -7718,7 +7718,7 @@
         </is>
       </c>
       <c r="D23" s="22" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="E23" s="22">
         <f>IF(D23&gt;22,D23-22,"")</f>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="D24" s="22" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="E24" s="22">
         <f>IF(D24&gt;22,D24-22,"")</f>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="D25" s="22" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="E25" s="22">
         <f>IF(D25&gt;22,D25-22,"")</f>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="D26" s="22" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="E26" s="22">
         <f>IF(D26&gt;22,D26-22,"")</f>
@@ -8574,7 +8574,7 @@
         </is>
       </c>
       <c r="D27" s="22" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="E27" s="22">
         <f>IF(D27&gt;22,D27-22,"")</f>
@@ -8789,7 +8789,7 @@
         </is>
       </c>
       <c r="D28" s="22" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="E28" s="22">
         <f>IF(D28&gt;22,D28-22,"")</f>
@@ -9004,7 +9004,7 @@
         </is>
       </c>
       <c r="D29" s="22" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="E29" s="22">
         <f>IF(D29&gt;22,D29-22,"")</f>
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="D30" s="22" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="E30" s="22">
         <f>IF(D30&gt;22,D30-22,"")</f>
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="D31" s="22" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="E31" s="22">
         <f>IF(D31&gt;22,D31-22,"")</f>
@@ -9645,7 +9645,7 @@
         </is>
       </c>
       <c r="D32" s="22" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="E32" s="22">
         <f>IF(D32&gt;22,D32-22,"")</f>
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="D33" s="22" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="E33" s="22">
         <f>IF(D33&gt;22,D33-22,"")</f>
@@ -10067,7 +10067,7 @@
         </is>
       </c>
       <c r="D34" s="22" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="E34" s="22">
         <f>IF(D34&gt;22,D34-22,"")</f>
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="D35" s="22" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="E35" s="22">
         <f>IF(D35&gt;22,D35-22,"")</f>
@@ -10493,7 +10493,7 @@
         </is>
       </c>
       <c r="D36" s="22" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="E36" s="22">
         <f>IF(D36&gt;22,D36-22,"")</f>
@@ -10708,7 +10708,7 @@
         </is>
       </c>
       <c r="D37" s="22" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="E37" s="22">
         <f>IF(D37&gt;22,D37-22,"")</f>
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="D38" s="22" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="E38" s="22">
         <f>IF(D38&gt;22,D38-22,"")</f>
@@ -11138,7 +11138,7 @@
         </is>
       </c>
       <c r="D39" s="22" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="E39" s="22">
         <f>IF(D39&gt;22,D39-22,"")</f>
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="D40" s="22" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="E40" s="22">
         <f>IF(D40&gt;22,D40-22,"")</f>
@@ -11568,7 +11568,7 @@
         </is>
       </c>
       <c r="D41" s="22" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="E41" s="22">
         <f>IF(D41&gt;22,D41-22,"")</f>
@@ -11783,7 +11783,7 @@
         </is>
       </c>
       <c r="D42" s="22" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="E42" s="22">
         <f>IF(D42&gt;22,D42-22,"")</f>
@@ -11998,7 +11998,7 @@
         </is>
       </c>
       <c r="D43" s="22" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="E43" s="22">
         <f>IF(D43&gt;22,D43-22,"")</f>
@@ -19780,7 +19780,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="E148">
         <f>IF(D148&gt;22,D148-22,"")</f>
@@ -19894,7 +19894,17 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>/Pic/uploads/Blue_1_20260929_020509.jpg</t>
+          <t>/Pic/uploads/Blue_1_20260929_184153.jpg</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Blue_2_20260929_184224.jpg</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Blue_3_20260929_184249.jpg</t>
         </is>
       </c>
       <c r="AG148" t="inlineStr">
@@ -20345,7 +20355,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="E151">
         <f>IF(D151&gt;22,D151-22,"")</f>
@@ -20535,7 +20545,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="E152">
         <f>IF(D152&gt;22,D152-22,"")</f>
@@ -20720,7 +20730,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="E153">
         <f>IF(D153&gt;22,D153-22,"")</f>
@@ -20913,6 +20923,7491 @@
         </is>
       </c>
       <c r="AW153" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154">
+        <f>IF(D154&gt;22,D154-22,"")</f>
+        <v/>
+      </c>
+      <c r="F154" t="n">
+        <v>499</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>285</v>
+      </c>
+      <c r="J154" t="n">
+        <v>10</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R154">
+        <f>IF(K154="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S154">
+        <f>IF(K154="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T154">
+        <f>IF(K154="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Teal</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>/Pic/DE26030/Black/Black_1.png</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>DE26_898300</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>DE26_898300103313</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Teal Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN154" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT154" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155">
+        <f>IF(D155&gt;22,D155-22,"")</f>
+        <v/>
+      </c>
+      <c r="F155" t="n">
+        <v>499</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>285</v>
+      </c>
+      <c r="J155" t="n">
+        <v>10</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R155">
+        <f>IF(K155="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S155">
+        <f>IF(K155="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T155">
+        <f>IF(K155="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>TESTDEL_CAD1F1</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>TESTDEL_CAD1F1103813</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Gold Maxi Women</t>
+        </is>
+      </c>
+      <c r="AN155" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT155" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156">
+        <f>IF(D156&gt;22,D156-22,"")</f>
+        <v/>
+      </c>
+      <c r="F156" t="n">
+        <v>499</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>285</v>
+      </c>
+      <c r="J156" t="n">
+        <v>15</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R156">
+        <f>IF(K156="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S156">
+        <f>IF(K156="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T156">
+        <f>IF(K156="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_1.jpg</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_2.jpg</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_3.jpg</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_4.jpg</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>TESTIMG_5434EA</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>TESTIMG_5434EA103613</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Blue Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN156" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT156" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Stylish Comfortable, Cotton Nighty for Women, Nighty, 100% Cotton Nighty, Summer Nighty, Nighty for Ladies, Nighty for girls, Floral Nighty, Pure cotton nighty, Maxi, Gown, Soft breathable sleepwear, Skin Friendly Nightdress.</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>284</v>
+      </c>
+      <c r="E157">
+        <f>IF(D157&gt;22,D157-22,"")</f>
+        <v/>
+      </c>
+      <c r="F157" t="n">
+        <v>449</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>285</v>
+      </c>
+      <c r="J157" t="n">
+        <v>6</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R157">
+        <f>IF(K157="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S157">
+        <f>IF(K157="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T157">
+        <f>IF(K157="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Brown_1_20260929_184348.jpg</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Brown_2_20260929_184356.jpg</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Brown_3_20260929_184416.jpg</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>DE26011B</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>DE26011B104013</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Upgrade your daily comfort with this printed nighty for women. Designed as a full-length maxi night gown, this sleeveless sleepwear offers a relaxed, flowing fit ideal for warm weather and daily home wear. The square neckline features contrast piping and a delicate center bow detail, complementing the all-over abstract print.</t>
+        </is>
+      </c>
+      <c r="AN157" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>Floral</t>
+        </is>
+      </c>
+      <c r="AT157" t="inlineStr">
+        <is>
+          <t>Short Sleeves</t>
+        </is>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158">
+        <f>IF(D158&gt;22,D158-22,"")</f>
+        <v/>
+      </c>
+      <c r="F158" t="n">
+        <v>499</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>285</v>
+      </c>
+      <c r="J158" t="n">
+        <v>10</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R158">
+        <f>IF(K158="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S158">
+        <f>IF(K158="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T158">
+        <f>IF(K158="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Teal</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>/Pic/DE26030/Black/Black_1.png</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>DE26_94DF66</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>DE26_94DF66103313</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Teal Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN158" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT158" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159">
+        <f>IF(D159&gt;22,D159-22,"")</f>
+        <v/>
+      </c>
+      <c r="F159" t="n">
+        <v>499</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>285</v>
+      </c>
+      <c r="J159" t="n">
+        <v>10</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R159">
+        <f>IF(K159="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S159">
+        <f>IF(K159="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T159">
+        <f>IF(K159="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>TESTDEL_2D6486</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>TESTDEL_2D6486103813</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Gold Maxi Women</t>
+        </is>
+      </c>
+      <c r="AN159" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT159" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160">
+        <f>IF(D160&gt;22,D160-22,"")</f>
+        <v/>
+      </c>
+      <c r="F160" t="n">
+        <v>499</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>285</v>
+      </c>
+      <c r="J160" t="n">
+        <v>15</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R160">
+        <f>IF(K160="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S160">
+        <f>IF(K160="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T160">
+        <f>IF(K160="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_1.jpg</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_2.jpg</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_3.jpg</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_4.jpg</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>TESTIMG_25027C</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>TESTIMG_25027C103613</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Blue Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN160" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT160" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Stylish Comfortable, Cotton Nighty for Women, Nighty, 100% Cotton Nighty, Summer Nighty, Nighty for Ladies, Nighty for girls, Floral Nighty, Pure cotton nighty, Maxi, Gown, Soft breathable sleepwear, Skin Friendly Nightdress.</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>284</v>
+      </c>
+      <c r="E161">
+        <f>IF(D161&gt;22,D161-22,"")</f>
+        <v/>
+      </c>
+      <c r="F161" t="n">
+        <v>449</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>285</v>
+      </c>
+      <c r="J161" t="n">
+        <v>6</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R161">
+        <f>IF(K161="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S161">
+        <f>IF(K161="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T161">
+        <f>IF(K161="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Green_1_20260929_184453.jpg</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Green_2_20260929_184500.jpg</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Green_3_20260929_184512.jpg</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>DE26011G</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>DE26011G103413</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Upgrade your daily comfort with this printed nighty for women. Designed as a full-length maxi night gown, this sleeveless sleepwear offers a relaxed, flowing fit ideal for warm weather and daily home wear. The square neckline features contrast piping and a delicate center bow detail, complementing the all-over abstract print.</t>
+        </is>
+      </c>
+      <c r="AN161" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>Floral</t>
+        </is>
+      </c>
+      <c r="AT161" t="inlineStr">
+        <is>
+          <t>Short Sleeves</t>
+        </is>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Stylish Comfortable, Cotton Nighty for Women, Nighty, 100% Cotton Nighty, Summer Nighty, Nighty for Ladies, Nighty for girls, Floral Nighty, Pure cotton nighty, Maxi, Gown, Soft breathable sleepwear, Skin Friendly Nightdress.</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>284</v>
+      </c>
+      <c r="E162">
+        <f>IF(D162&gt;22,D162-22,"")</f>
+        <v/>
+      </c>
+      <c r="F162" t="n">
+        <v>449</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>285</v>
+      </c>
+      <c r="J162" t="n">
+        <v>6</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R162">
+        <f>IF(K162="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S162">
+        <f>IF(K162="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T162">
+        <f>IF(K162="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Pink</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Pink_1_20260929_184547.jpg</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Pink_2_20260929_184555.jpg</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Pink_3_20260929_184601.jpg</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>DE26011P</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>DE26011P101413</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Upgrade your daily comfort with this printed nighty for women. Designed as a full-length maxi night gown, this sleeveless sleepwear offers a relaxed, flowing fit ideal for warm weather and daily home wear. The square neckline features contrast piping and a delicate center bow detail, complementing the all-over abstract print.</t>
+        </is>
+      </c>
+      <c r="AN162" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>Floral</t>
+        </is>
+      </c>
+      <c r="AT162" t="inlineStr">
+        <is>
+          <t>Short Sleeves</t>
+        </is>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Stylish Comfortable, Cotton Nighty for Women, Nighty, 100% Cotton Nighty, Summer Nighty, Nighty for Ladies, Nighty for girls, Floral Nighty, Pure cotton nighty, Maxi, Gown, Soft breathable sleepwear, Skin Friendly Nightdress.</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>284</v>
+      </c>
+      <c r="E163">
+        <f>IF(D163&gt;22,D163-22,"")</f>
+        <v/>
+      </c>
+      <c r="F163" t="n">
+        <v>449</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>285</v>
+      </c>
+      <c r="J163" t="n">
+        <v>5</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R163">
+        <f>IF(K163="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S163">
+        <f>IF(K163="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T163">
+        <f>IF(K163="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Red_1_20260929_184638.jpg</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Red_2_20260929_184650.jpg</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Red_3_20260929_184657.jpg</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>DE26011R</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>DE26011R101213</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Upgrade your daily comfort with this printed nighty for women. Designed as a full-length maxi night gown, this sleeveless sleepwear offers a relaxed, flowing fit ideal for warm weather and daily home wear. The square neckline features contrast piping and a delicate center bow detail, complementing the all-over abstract print.</t>
+        </is>
+      </c>
+      <c r="AN163" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>Floral</t>
+        </is>
+      </c>
+      <c r="AT163" t="inlineStr">
+        <is>
+          <t>Short Sleeves</t>
+        </is>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164">
+        <f>IF(D164&gt;22,D164-22,"")</f>
+        <v/>
+      </c>
+      <c r="F164" t="n">
+        <v>499</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>285</v>
+      </c>
+      <c r="J164" t="n">
+        <v>10</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R164">
+        <f>IF(K164="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S164">
+        <f>IF(K164="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T164">
+        <f>IF(K164="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Teal</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>/Pic/DE26030/Black/Black_1.png</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>DE26_034F2B</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>DE26_034F2B103313</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Teal Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN164" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT164" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165">
+        <f>IF(D165&gt;22,D165-22,"")</f>
+        <v/>
+      </c>
+      <c r="F165" t="n">
+        <v>499</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>285</v>
+      </c>
+      <c r="J165" t="n">
+        <v>10</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R165">
+        <f>IF(K165="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S165">
+        <f>IF(K165="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T165">
+        <f>IF(K165="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>TESTDEL_9F1C59</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>TESTDEL_9F1C59103813</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Gold Maxi Women</t>
+        </is>
+      </c>
+      <c r="AN165" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT165" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166">
+        <f>IF(D166&gt;22,D166-22,"")</f>
+        <v/>
+      </c>
+      <c r="F166" t="n">
+        <v>499</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>285</v>
+      </c>
+      <c r="J166" t="n">
+        <v>15</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R166">
+        <f>IF(K166="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S166">
+        <f>IF(K166="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T166">
+        <f>IF(K166="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_1.jpg</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_2.jpg</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_3.jpg</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_4.jpg</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>TESTIMG_89EBE7</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>TESTIMG_89EBE7103613</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Blue Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN166" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT166" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167">
+        <f>IF(D167&gt;22,D167-22,"")</f>
+        <v/>
+      </c>
+      <c r="F167" t="n">
+        <v>499</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>285</v>
+      </c>
+      <c r="J167" t="n">
+        <v>10</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R167">
+        <f>IF(K167="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S167">
+        <f>IF(K167="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T167">
+        <f>IF(K167="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Teal</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>/Pic/DE26030/Black/Black_1.png</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>DE26_A881F3</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>DE26_A881F3103313</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Teal Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN167" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT167" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168">
+        <f>IF(D168&gt;22,D168-22,"")</f>
+        <v/>
+      </c>
+      <c r="F168" t="n">
+        <v>499</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>285</v>
+      </c>
+      <c r="J168" t="n">
+        <v>10</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R168">
+        <f>IF(K168="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S168">
+        <f>IF(K168="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T168">
+        <f>IF(K168="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>TESTDEL_E96E1F</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>TESTDEL_E96E1F103813</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Gold Maxi Women</t>
+        </is>
+      </c>
+      <c r="AN168" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT168" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169">
+        <f>IF(D169&gt;22,D169-22,"")</f>
+        <v/>
+      </c>
+      <c r="F169" t="n">
+        <v>499</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>285</v>
+      </c>
+      <c r="J169" t="n">
+        <v>15</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R169">
+        <f>IF(K169="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S169">
+        <f>IF(K169="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T169">
+        <f>IF(K169="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_1.jpg</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_2.jpg</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_3.jpg</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_4.jpg</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>TESTIMG_83797E</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>TESTIMG_83797E103613</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Blue Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN169" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT169" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Stylish Comfortable, Cotton Nighty for Women, Nighty, 100% Cotton Nighty, Summer Nighty, Nighty for Ladies, Nighty for girls, Floral Nighty, Pure cotton nighty, Maxi, Gown, Soft breathable sleepwear, Skin Friendly Nightdress.</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>284</v>
+      </c>
+      <c r="E170">
+        <f>IF(D170&gt;22,D170-22,"")</f>
+        <v/>
+      </c>
+      <c r="F170" t="n">
+        <v>449</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>290</v>
+      </c>
+      <c r="J170" t="n">
+        <v>6</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R170">
+        <f>IF(K170="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S170">
+        <f>IF(K170="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T170">
+        <f>IF(K170="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Brown_1_20260929_174415.jpg</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Brown_2_20260929_174424.jpg</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Brown_3_20260929_174430.jpg</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>DE26010B</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>DE26010B104013</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Upgrade your daily comfort with this printed nighty for women. Designed as a full-length maxi night gown, this sleeveless sleepwear offers a relaxed, flowing fit ideal for warm weather and daily home wear. The square neckline features contrast piping and a delicate center bow detail, complementing the all-over abstract print.</t>
+        </is>
+      </c>
+      <c r="AN170" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>Floral</t>
+        </is>
+      </c>
+      <c r="AT170" t="inlineStr">
+        <is>
+          <t>Short Sleeves</t>
+        </is>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Stylish Comfortable, Cotton Nighty for Women, Nighty, 100% Cotton Nighty, Summer Nighty, Nighty for Ladies, Nighty for girls, Floral Nighty, Pure cotton nighty, Maxi, Gown, Soft breathable sleepwear, Skin Friendly Nightdress.</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>284</v>
+      </c>
+      <c r="E171">
+        <f>IF(D171&gt;22,D171-22,"")</f>
+        <v/>
+      </c>
+      <c r="F171" t="n">
+        <v>449</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>290</v>
+      </c>
+      <c r="J171" t="n">
+        <v>6</v>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R171">
+        <f>IF(K171="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S171">
+        <f>IF(K171="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T171">
+        <f>IF(K171="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Green_1_20260929_175012.jpg</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Green_2_20260929_175018.jpg</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Green_3_20260929_175023.jpg</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>DE26010G</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>DE26010G103413</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Upgrade your daily comfort with this printed nighty for women. Designed as a full-length maxi night gown, this sleeveless sleepwear offers a relaxed, flowing fit ideal for warm weather and daily home wear. The square neckline features contrast piping and a delicate center bow detail, complementing the all-over abstract print.</t>
+        </is>
+      </c>
+      <c r="AN171" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>Floral</t>
+        </is>
+      </c>
+      <c r="AT171" t="inlineStr">
+        <is>
+          <t>Short Sleeves</t>
+        </is>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Stylish Comfortable, Cotton Nighty for Women, Nighty, 100% Cotton Nighty, Summer Nighty, Nighty for Ladies, Nighty for girls, Floral Nighty, Pure cotton nighty, Maxi, Gown, Soft breathable sleepwear, Skin Friendly Nightdress.</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>284</v>
+      </c>
+      <c r="E172">
+        <f>IF(D172&gt;22,D172-22,"")</f>
+        <v/>
+      </c>
+      <c r="F172" t="n">
+        <v>449</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>290</v>
+      </c>
+      <c r="J172" t="n">
+        <v>6</v>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R172">
+        <f>IF(K172="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S172">
+        <f>IF(K172="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T172">
+        <f>IF(K172="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Maroon</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Maroon_1_20260929_181714.jpg</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Maroon_2_20260929_181729.jpg</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Maroon_3_20260929_181737.jpg</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>DE26010M</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>DE26010M103213</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Upgrade your daily comfort with this printed nighty for women. Designed as a full-length maxi night gown, this sleeveless sleepwear offers a relaxed, flowing fit ideal for warm weather and daily home wear. The square neckline features contrast piping and a delicate center bow detail, complementing the all-over abstract print.</t>
+        </is>
+      </c>
+      <c r="AN172" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>Floral</t>
+        </is>
+      </c>
+      <c r="AT172" t="inlineStr">
+        <is>
+          <t>Short Sleeves</t>
+        </is>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Stylish Comfortable, Cotton Nighty for Women, Nighty, 100% Cotton Nighty, Summer Nighty, Nighty for Ladies, Nighty for girls, Floral Nighty, Pure cotton nighty, Maxi, Gown, Soft breathable sleepwear, Skin Friendly Nightdress.</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>284</v>
+      </c>
+      <c r="E173">
+        <f>IF(D173&gt;22,D173-22,"")</f>
+        <v/>
+      </c>
+      <c r="F173" t="n">
+        <v>449</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>290</v>
+      </c>
+      <c r="J173" t="n">
+        <v>6</v>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R173">
+        <f>IF(K173="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S173">
+        <f>IF(K173="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T173">
+        <f>IF(K173="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Navy Blue</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Navy_Blue_1_20260929_182253.jpg</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Navy_Blue_2_20260929_182259.jpg</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Navy_Blue_3_20260929_182305.jpg</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>DE26010N</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>DE26010N101313</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Upgrade your daily comfort with this printed nighty for women. Designed as a full-length maxi night gown, this sleeveless sleepwear offers a relaxed, flowing fit ideal for warm weather and daily home wear. The square neckline features contrast piping and a delicate center bow detail, complementing the all-over abstract print.</t>
+        </is>
+      </c>
+      <c r="AN173" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>Floral</t>
+        </is>
+      </c>
+      <c r="AT173" t="inlineStr">
+        <is>
+          <t>Short Sleeves</t>
+        </is>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Stylish Comfortable, Cotton Nighty for Women, Nighty, 100% Cotton Nighty, Summer Nighty, Nighty for Ladies, Nighty for girls, Floral Nighty, Pure cotton nighty, Maxi, Gown, Soft breathable sleepwear, Skin Friendly Nightdress.</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>284</v>
+      </c>
+      <c r="E174">
+        <f>IF(D174&gt;22,D174-22,"")</f>
+        <v/>
+      </c>
+      <c r="F174" t="n">
+        <v>449</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>290</v>
+      </c>
+      <c r="J174" t="n">
+        <v>6</v>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R174">
+        <f>IF(K174="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S174">
+        <f>IF(K174="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T174">
+        <f>IF(K174="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Red_1_20260929_182834.jpg</t>
+        </is>
+      </c>
+      <c r="AD174" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Red_2_20260929_182840.jpg</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/Red_3_20260929_182845.jpg</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>DE26010R</t>
+        </is>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>DE26010R101213</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>Upgrade your daily comfort with this printed nighty for women. Designed as a full-length maxi night gown, this sleeveless sleepwear offers a relaxed, flowing fit ideal for warm weather and daily home wear. The square neckline features contrast piping and a delicate center bow detail, complementing the all-over abstract print.</t>
+        </is>
+      </c>
+      <c r="AN174" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>Floral</t>
+        </is>
+      </c>
+      <c r="AT174" t="inlineStr">
+        <is>
+          <t>Short Sleeves</t>
+        </is>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV174" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175">
+        <f>IF(D175&gt;22,D175-22,"")</f>
+        <v/>
+      </c>
+      <c r="F175" t="n">
+        <v>499</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>285</v>
+      </c>
+      <c r="J175" t="n">
+        <v>10</v>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R175">
+        <f>IF(K175="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S175">
+        <f>IF(K175="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T175">
+        <f>IF(K175="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Teal</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>/Pic/DE26030/Black/Black_1.png</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>DE26_A47038</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>DE26_A47038103313</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Teal Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN175" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT175" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176">
+        <f>IF(D176&gt;22,D176-22,"")</f>
+        <v/>
+      </c>
+      <c r="F176" t="n">
+        <v>499</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>285</v>
+      </c>
+      <c r="J176" t="n">
+        <v>10</v>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R176">
+        <f>IF(K176="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S176">
+        <f>IF(K176="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T176">
+        <f>IF(K176="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>TESTDEL_2EAD12</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>TESTDEL_2EAD12103813</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Gold Maxi Women</t>
+        </is>
+      </c>
+      <c r="AN176" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT176" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV176" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177">
+        <f>IF(D177&gt;22,D177-22,"")</f>
+        <v/>
+      </c>
+      <c r="F177" t="n">
+        <v>499</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>285</v>
+      </c>
+      <c r="J177" t="n">
+        <v>15</v>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R177">
+        <f>IF(K177="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S177">
+        <f>IF(K177="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T177">
+        <f>IF(K177="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_1.jpg</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_2.jpg</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_3.jpg</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_4.jpg</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>TESTIMG_130CE2</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>TESTIMG_130CE2103613</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Blue Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN177" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT177" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178">
+        <f>IF(D178&gt;22,D178-22,"")</f>
+        <v/>
+      </c>
+      <c r="F178" t="n">
+        <v>499</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>285</v>
+      </c>
+      <c r="J178" t="n">
+        <v>10</v>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R178">
+        <f>IF(K178="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S178">
+        <f>IF(K178="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T178">
+        <f>IF(K178="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Teal</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>/Pic/DE26030/Black/Black_1.png</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>DE26_B79C0C</t>
+        </is>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>DE26_B79C0C103313</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Teal Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN178" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT178" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179">
+        <f>IF(D179&gt;22,D179-22,"")</f>
+        <v/>
+      </c>
+      <c r="F179" t="n">
+        <v>499</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>285</v>
+      </c>
+      <c r="J179" t="n">
+        <v>10</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R179">
+        <f>IF(K179="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S179">
+        <f>IF(K179="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T179">
+        <f>IF(K179="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>TESTDEL_B61EA2</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>TESTDEL_B61EA2103813</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Gold Maxi Women</t>
+        </is>
+      </c>
+      <c r="AN179" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP179" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT179" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV179" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180">
+        <f>IF(D180&gt;22,D180-22,"")</f>
+        <v/>
+      </c>
+      <c r="F180" t="n">
+        <v>499</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>285</v>
+      </c>
+      <c r="J180" t="n">
+        <v>15</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R180">
+        <f>IF(K180="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S180">
+        <f>IF(K180="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T180">
+        <f>IF(K180="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_1.jpg</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_2.jpg</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_3.jpg</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_4.jpg</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>TESTIMG_297FAE</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>TESTIMG_297FAE103613</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Blue Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN180" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP180" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT180" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV180" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Stylish Comfortable, Cotton Nighty for Women, Nighty, 100% Cotton Nighty, Summer Nighty, Nighty for Ladies, Nighty for girls, Floral Nighty, Pure cotton nighty, Maxi, Gown, Soft breathable sleepwear, Skin Friendly Nightdress.</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>345</v>
+      </c>
+      <c r="E181">
+        <f>IF(D181&gt;22,D181-22,"")</f>
+        <v/>
+      </c>
+      <c r="F181" t="n">
+        <v>599</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>285</v>
+      </c>
+      <c r="J181" t="n">
+        <v>12</v>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R181">
+        <f>IF(K181="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S181">
+        <f>IF(K181="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T181">
+        <f>IF(K181="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/All_Pages-2_20261005_182548.jpg</t>
+        </is>
+      </c>
+      <c r="AD181" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/All_Pages-3_20261005_182554.jpg</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/All_Pages-4_20261005_182609.jpg</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/All_Pages-5_20261005_182618.jpg</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>DE26012K</t>
+        </is>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>DE26012K103313</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>Upgrade your daily comfort with this printed nighty for women. Designed as a full-length maxi night gown, this sleeveless sleepwear offers a relaxed, flowing fit ideal for warm weather and daily home wear. The square neckline features contrast piping and a delicate center bow detail, complementing the all-over abstract print.</t>
+        </is>
+      </c>
+      <c r="AN181" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>Stylised</t>
+        </is>
+      </c>
+      <c r="AP181" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>Floral</t>
+        </is>
+      </c>
+      <c r="AT181" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU181" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV181" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Stylish Comfortable, Cotton Nighty for Women, Nighty, 100% Cotton Nighty, Summer Nighty, Nighty for Ladies, Nighty for girls, Floral Nighty, Pure cotton nighty, Maxi, Gown, Soft breathable sleepwear, Skin Friendly Nightdress.</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>342</v>
+      </c>
+      <c r="E182">
+        <f>IF(D182&gt;22,D182-22,"")</f>
+        <v/>
+      </c>
+      <c r="F182" t="n">
+        <v>599</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>285</v>
+      </c>
+      <c r="J182" t="n">
+        <v>12</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post., Barasat, West Bengal - 700125</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R182">
+        <f>IF(K182="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S182">
+        <f>IF(K182="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T182">
+        <f>IF(K182="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/All_Pages-6_20261005_183407.jpg</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/All_Pages-7_20261005_183412.jpg</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/All_Pages-8_20261005_183417.jpg</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>/Pic/uploads/All_Pages-9_20261005_183425.jpg</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>DE26012B</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>DE26012B103613</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Upgrade your daily comfort with this printed nighty for women. Designed as a full-length maxi night gown, this sleeveless sleepwear offers a relaxed, flowing fit ideal for warm weather and daily home wear. The square neckline features contrast piping and a delicate center bow detail, complementing the all-over abstract print.</t>
+        </is>
+      </c>
+      <c r="AN182" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>Stylised</t>
+        </is>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>Ethnic Motif</t>
+        </is>
+      </c>
+      <c r="AT182" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV182" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183">
+        <f>IF(D183&gt;22,D183-22,"")</f>
+        <v/>
+      </c>
+      <c r="F183" t="n">
+        <v>499</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>285</v>
+      </c>
+      <c r="J183" t="n">
+        <v>10</v>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R183">
+        <f>IF(K183="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S183">
+        <f>IF(K183="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T183">
+        <f>IF(K183="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Teal</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>/Pic/DE26030/Black/Black_1.png</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>DE26_FF9631</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>DE26_FF9631103313</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Teal Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN183" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP183" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ183" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT183" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU183" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV183" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184">
+        <f>IF(D184&gt;22,D184-22,"")</f>
+        <v/>
+      </c>
+      <c r="F184" t="n">
+        <v>499</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>285</v>
+      </c>
+      <c r="J184" t="n">
+        <v>10</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R184">
+        <f>IF(K184="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S184">
+        <f>IF(K184="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T184">
+        <f>IF(K184="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>TESTDEL_D318F3</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>TESTDEL_D318F3103813</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Gold Maxi Women</t>
+        </is>
+      </c>
+      <c r="AN184" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP184" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT184" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU184" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV184" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185">
+        <f>IF(D185&gt;22,D185-22,"")</f>
+        <v/>
+      </c>
+      <c r="F185" t="n">
+        <v>499</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>285</v>
+      </c>
+      <c r="J185" t="n">
+        <v>15</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R185">
+        <f>IF(K185="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S185">
+        <f>IF(K185="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T185">
+        <f>IF(K185="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_1.jpg</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_2.jpg</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_3.jpg</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_4.jpg</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>TESTIMG_3D9312</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>TESTIMG_3D9312103613</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Blue Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN185" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP185" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ185" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT185" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU185" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV185" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186">
+        <f>IF(D186&gt;22,D186-22,"")</f>
+        <v/>
+      </c>
+      <c r="F186" t="n">
+        <v>499</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>285</v>
+      </c>
+      <c r="J186" t="n">
+        <v>10</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R186">
+        <f>IF(K186="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S186">
+        <f>IF(K186="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T186">
+        <f>IF(K186="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Teal</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>/Pic/DE26030/Black/Black_1.png</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>DE26_D5F52E</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>DE26_D5F52E103313</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Teal Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN186" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP186" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT186" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV186" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187">
+        <f>IF(D187&gt;22,D187-22,"")</f>
+        <v/>
+      </c>
+      <c r="F187" t="n">
+        <v>499</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>285</v>
+      </c>
+      <c r="J187" t="n">
+        <v>10</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R187">
+        <f>IF(K187="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S187">
+        <f>IF(K187="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T187">
+        <f>IF(K187="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>TESTDEL_09285F</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>TESTDEL_09285F103813</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Gold Maxi Women</t>
+        </is>
+      </c>
+      <c r="AN187" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP187" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT187" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU187" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV187" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188">
+        <f>IF(D188&gt;22,D188-22,"")</f>
+        <v/>
+      </c>
+      <c r="F188" t="n">
+        <v>499</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>285</v>
+      </c>
+      <c r="J188" t="n">
+        <v>15</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R188">
+        <f>IF(K188="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S188">
+        <f>IF(K188="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T188">
+        <f>IF(K188="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_1.jpg</t>
+        </is>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_2.jpg</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_3.jpg</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_4.jpg</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>TESTIMG_6855A1</t>
+        </is>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>TESTIMG_6855A1103613</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Blue Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN188" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP188" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT188" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV188" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>340</v>
+      </c>
+      <c r="E189">
+        <f>IF(D189&gt;22,D189-22,"")</f>
+        <v/>
+      </c>
+      <c r="F189" t="n">
+        <v>499</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>285</v>
+      </c>
+      <c r="J189" t="n">
+        <v>10</v>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R189">
+        <f>IF(K189="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S189">
+        <f>IF(K189="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T189">
+        <f>IF(K189="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Teal</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>/Pic/DE26030/Black/Black_1.png</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>DE26_C7F704</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>DE26_C7F704103313</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Teal Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN189" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP189" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT189" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU189" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV189" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>240</v>
+      </c>
+      <c r="E190">
+        <f>IF(D190&gt;22,D190-22,"")</f>
+        <v/>
+      </c>
+      <c r="F190" t="n">
+        <v>499</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>285</v>
+      </c>
+      <c r="J190" t="n">
+        <v>10</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R190">
+        <f>IF(K190="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S190">
+        <f>IF(K190="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T190">
+        <f>IF(K190="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>TESTDEL_85BE32</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>TESTDEL_85BE32103813</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Gold Maxi Women</t>
+        </is>
+      </c>
+      <c r="AN190" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP190" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT190" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU190" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV190" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>280</v>
+      </c>
+      <c r="E191">
+        <f>IF(D191&gt;22,D191-22,"")</f>
+        <v/>
+      </c>
+      <c r="F191" t="n">
+        <v>499</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>620821</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>285</v>
+      </c>
+      <c r="J191" t="n">
+        <v>15</v>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Pegasus Creation</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Divine Enterprise</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Prasanta Apartment, Check Post</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>700125</t>
+        </is>
+      </c>
+      <c r="R191">
+        <f>IF(K191="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="S191">
+        <f>IF(K191="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="T191">
+        <f>IF(K191="India","Not Required","")</f>
+        <v/>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>No Add Ons</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_1.jpg</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_2.jpg</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_3.jpg</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>/Pic/DE26011/Blue/Blue_4.jpg</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>TESTIMG_47F849</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>TESTIMG_47F849103613</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Divine Enterprise Blue Square Neck Nighty</t>
+        </is>
+      </c>
+      <c r="AN191" t="inlineStr">
+        <is>
+          <t>Maxi</t>
+        </is>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>Square Neck</t>
+        </is>
+      </c>
+      <c r="AP191" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>No Pocket</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>Botanical</t>
+        </is>
+      </c>
+      <c r="AT191" t="inlineStr">
+        <is>
+          <t>Sleeveless</t>
+        </is>
+      </c>
+      <c r="AU191" t="inlineStr">
+        <is>
+          <t>Pleated Or Gathered</t>
+        </is>
+      </c>
+      <c r="AV191" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AW191" t="inlineStr">
         <is>
           <t>36</t>
         </is>
